--- a/ig/DM_FINESS_New/ValueSet-jdv-j293-type-engagement-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j293-type-engagement-finess.xlsx
@@ -30,7 +30,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>OID:1.2.250.1.213.1.6.1.265</t>
+    <t>OID:1.2.250.1.213.1.6.1.267</t>
   </si>
   <si>
     <t>Version</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j293-type-engagement-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j293-type-engagement-finess.xlsx
@@ -96,13 +96,13 @@
     <t>Operation</t>
   </si>
   <si>
-    <t>finess</t>
+    <t>niveau</t>
   </si>
   <si>
     <t>=</t>
   </si>
   <si>
-    <t>true</t>
+    <t>1</t>
   </si>
   <si>
     <t/>
@@ -111,7 +111,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r363-type-engagement</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r395-engagement</t>
   </si>
 </sst>
 </file>
